--- a/buckman/output/depletion/TABLE_4_Rio_Grande_Otowi_2024.xlsx
+++ b/buckman/output/depletion/TABLE_4_Rio_Grande_Otowi_2024.xlsx
@@ -3422,53 +3422,41 @@
           <t>Rio Grande above Otowi</t>
         </is>
       </c>
-      <c r="F53" s="4">
-        <f>SUM(F20:F29)</f>
-        <v/>
-      </c>
-      <c r="G53" s="4">
-        <f>SUM(G20:G29)</f>
-        <v/>
-      </c>
-      <c r="H53" s="4">
-        <f>SUM(H20:H29)</f>
-        <v/>
-      </c>
-      <c r="I53" s="4">
-        <f>SUM(I20:I29)</f>
-        <v/>
-      </c>
-      <c r="J53" s="4">
-        <f>SUM(J20:J29)</f>
-        <v/>
-      </c>
-      <c r="K53" s="4">
-        <f>SUM(K20:K29)</f>
-        <v/>
-      </c>
-      <c r="L53" s="4">
-        <f>SUM(L20:L29)</f>
-        <v/>
-      </c>
-      <c r="M53" s="4">
-        <f>SUM(M20:M29)</f>
-        <v/>
-      </c>
-      <c r="N53" s="4">
-        <f>SUM(N20:N29)</f>
-        <v/>
-      </c>
-      <c r="O53" s="4">
-        <f>SUM(O20:O29)</f>
-        <v/>
-      </c>
-      <c r="P53" s="4">
-        <f>SUM(P20:P29)</f>
-        <v/>
-      </c>
-      <c r="Q53" s="4">
-        <f>SUM(Q20:Q29)</f>
-        <v/>
+      <c r="F53" s="4" t="n">
+        <v>0.140315</v>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>0.140025</v>
+      </c>
+      <c r="H53" s="4" t="n">
+        <v>0.139714</v>
+      </c>
+      <c r="I53" s="4" t="n">
+        <v>0.139441</v>
+      </c>
+      <c r="J53" s="4" t="n">
+        <v>0.13924</v>
+      </c>
+      <c r="K53" s="4" t="n">
+        <v>0.13918</v>
+      </c>
+      <c r="L53" s="4" t="n">
+        <v>0.139358</v>
+      </c>
+      <c r="M53" s="4" t="n">
+        <v>0.139807</v>
+      </c>
+      <c r="N53" s="4" t="n">
+        <v>0.140353</v>
+      </c>
+      <c r="O53" s="4" t="n">
+        <v>0.140912</v>
+      </c>
+      <c r="P53" s="4" t="n">
+        <v>0.141305</v>
+      </c>
+      <c r="Q53" s="4" t="n">
+        <v>0.141521</v>
       </c>
     </row>
     <row r="54">
@@ -3477,53 +3465,41 @@
           <t>Rio Grande below Otowi</t>
         </is>
       </c>
-      <c r="F54" s="4">
-        <f>SUM(F30:F45)</f>
-        <v/>
-      </c>
-      <c r="G54" s="4">
-        <f>SUM(G30:G45)</f>
-        <v/>
-      </c>
-      <c r="H54" s="4">
-        <f>SUM(H30:H45)</f>
-        <v/>
-      </c>
-      <c r="I54" s="4">
-        <f>SUM(I30:I45)</f>
-        <v/>
-      </c>
-      <c r="J54" s="4">
-        <f>SUM(J30:J45)</f>
-        <v/>
-      </c>
-      <c r="K54" s="4">
-        <f>SUM(K30:K45)</f>
-        <v/>
-      </c>
-      <c r="L54" s="4">
-        <f>SUM(L30:L45)</f>
-        <v/>
-      </c>
-      <c r="M54" s="4">
-        <f>SUM(M30:M45)</f>
-        <v/>
-      </c>
-      <c r="N54" s="4">
-        <f>SUM(N30:N45)</f>
-        <v/>
-      </c>
-      <c r="O54" s="4">
-        <f>SUM(O30:O45)</f>
-        <v/>
-      </c>
-      <c r="P54" s="4">
-        <f>SUM(P30:P45)</f>
-        <v/>
-      </c>
-      <c r="Q54" s="4">
-        <f>SUM(Q30:Q45)</f>
-        <v/>
+      <c r="F54" s="4" t="n">
+        <v>0.9075450000000002</v>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>0.939872</v>
+      </c>
+      <c r="H54" s="4" t="n">
+        <v>0.898105</v>
+      </c>
+      <c r="I54" s="4" t="n">
+        <v>0.9410000000000002</v>
+      </c>
+      <c r="J54" s="4" t="n">
+        <v>1.026514</v>
+      </c>
+      <c r="K54" s="4" t="n">
+        <v>1.124673</v>
+      </c>
+      <c r="L54" s="4" t="n">
+        <v>1.384959</v>
+      </c>
+      <c r="M54" s="4" t="n">
+        <v>1.502795000000001</v>
+      </c>
+      <c r="N54" s="4" t="n">
+        <v>1.419017</v>
+      </c>
+      <c r="O54" s="4" t="n">
+        <v>1.392248</v>
+      </c>
+      <c r="P54" s="4" t="n">
+        <v>1.222206</v>
+      </c>
+      <c r="Q54" s="4" t="n">
+        <v>1.193105</v>
       </c>
     </row>
     <row r="55">
@@ -3604,57 +3580,44 @@
           <t>Above Otowi</t>
         </is>
       </c>
-      <c r="F56" s="6">
-        <f>F53*60*60*24*F$52/43560</f>
-        <v/>
-      </c>
-      <c r="G56" s="6">
-        <f>G53*60*60*24*G$52/43560</f>
-        <v/>
-      </c>
-      <c r="H56" s="6">
-        <f>H53*60*60*24*H$52/43560</f>
-        <v/>
-      </c>
-      <c r="I56" s="6">
-        <f>I53*60*60*24*I$52/43560</f>
-        <v/>
-      </c>
-      <c r="J56" s="6">
-        <f>J53*60*60*24*J$52/43560</f>
-        <v/>
-      </c>
-      <c r="K56" s="6">
-        <f>K53*60*60*24*K$52/43560</f>
-        <v/>
-      </c>
-      <c r="L56" s="6">
-        <f>L53*60*60*24*L$52/43560</f>
-        <v/>
-      </c>
-      <c r="M56" s="6">
-        <f>M53*60*60*24*M$52/43560</f>
-        <v/>
-      </c>
-      <c r="N56" s="6">
-        <f>N53*60*60*24*N$52/43560</f>
-        <v/>
-      </c>
-      <c r="O56" s="6">
-        <f>O53*60*60*24*O$52/43560</f>
-        <v/>
-      </c>
-      <c r="P56" s="6">
-        <f>P53*60*60*24*P$52/43560</f>
-        <v/>
-      </c>
-      <c r="Q56" s="6">
-        <f>Q53*60*60*24*Q$52/43560</f>
-        <v/>
-      </c>
-      <c r="R56" s="7">
-        <f>SUM(F56:Q56)</f>
-        <v/>
+      <c r="F56" s="6" t="n">
+        <v>8.627633057851241</v>
+      </c>
+      <c r="G56" s="6" t="n">
+        <v>7.776595041322314</v>
+      </c>
+      <c r="H56" s="6" t="n">
+        <v>8.590679008264464</v>
+      </c>
+      <c r="I56" s="6" t="n">
+        <v>8.297315702479338</v>
+      </c>
+      <c r="J56" s="6" t="n">
+        <v>8.561533884297521</v>
+      </c>
+      <c r="K56" s="6" t="n">
+        <v>8.281785123966943</v>
+      </c>
+      <c r="L56" s="6" t="n">
+        <v>8.568789421487605</v>
+      </c>
+      <c r="M56" s="6" t="n">
+        <v>8.5963973553719</v>
+      </c>
+      <c r="N56" s="6" t="n">
+        <v>8.351583471074379</v>
+      </c>
+      <c r="O56" s="6" t="n">
+        <v>8.664341157024792</v>
+      </c>
+      <c r="P56" s="6" t="n">
+        <v>8.408231404958679</v>
+      </c>
+      <c r="Q56" s="6" t="n">
+        <v>8.701787107438017</v>
+      </c>
+      <c r="R56" s="7" t="n">
+        <v>101.4266717355372</v>
       </c>
     </row>
     <row r="57">
@@ -3668,57 +3631,44 @@
           <t>Below Otowi</t>
         </is>
       </c>
-      <c r="F57" s="6">
-        <f>F54*60*60*24*F$52/43560</f>
-        <v/>
-      </c>
-      <c r="G57" s="6">
-        <f>G54*60*60*24*G$52/43560</f>
-        <v/>
-      </c>
-      <c r="H57" s="6">
-        <f>H54*60*60*24*H$52/43560</f>
-        <v/>
-      </c>
-      <c r="I57" s="6">
-        <f>I54*60*60*24*I$52/43560</f>
-        <v/>
-      </c>
-      <c r="J57" s="6">
-        <f>J54*60*60*24*J$52/43560</f>
-        <v/>
-      </c>
-      <c r="K57" s="6">
-        <f>K54*60*60*24*K$52/43560</f>
-        <v/>
-      </c>
-      <c r="L57" s="6">
-        <f>L54*60*60*24*L$52/43560</f>
-        <v/>
-      </c>
-      <c r="M57" s="6">
-        <f>M54*60*60*24*M$52/43560</f>
-        <v/>
-      </c>
-      <c r="N57" s="6">
-        <f>N54*60*60*24*N$52/43560</f>
-        <v/>
-      </c>
-      <c r="O57" s="6">
-        <f>O54*60*60*24*O$52/43560</f>
-        <v/>
-      </c>
-      <c r="P57" s="6">
-        <f>P54*60*60*24*P$52/43560</f>
-        <v/>
-      </c>
-      <c r="Q57" s="6">
-        <f>Q54*60*60*24*Q$52/43560</f>
-        <v/>
-      </c>
-      <c r="R57" s="7">
-        <f>SUM(F57:Q57)</f>
-        <v/>
+      <c r="F57" s="6" t="n">
+        <v>55.80276694214877</v>
+      </c>
+      <c r="G57" s="6" t="n">
+        <v>52.19784991735537</v>
+      </c>
+      <c r="H57" s="6" t="n">
+        <v>55.22232396694215</v>
+      </c>
+      <c r="I57" s="6" t="n">
+        <v>55.99338842975207</v>
+      </c>
+      <c r="J57" s="6" t="n">
+        <v>63.11788561983472</v>
+      </c>
+      <c r="K57" s="6" t="n">
+        <v>66.92269090909089</v>
+      </c>
+      <c r="L57" s="6" t="n">
+        <v>85.15780958677686</v>
+      </c>
+      <c r="M57" s="6" t="n">
+        <v>92.40326280991739</v>
+      </c>
+      <c r="N57" s="6" t="n">
+        <v>84.43737520661159</v>
+      </c>
+      <c r="O57" s="6" t="n">
+        <v>85.60599272727271</v>
+      </c>
+      <c r="P57" s="6" t="n">
+        <v>72.72630743801655</v>
+      </c>
+      <c r="Q57" s="6" t="n">
+        <v>73.36116694214876</v>
+      </c>
+      <c r="R57" s="7" t="n">
+        <v>842.9488204958678</v>
       </c>
     </row>
     <row r="58">
@@ -3727,53 +3677,41 @@
           <t>Total RG (sum)</t>
         </is>
       </c>
-      <c r="F58" s="6">
-        <f>SUM(F56:F57)</f>
-        <v/>
-      </c>
-      <c r="G58" s="6">
-        <f>SUM(G56:G57)</f>
-        <v/>
-      </c>
-      <c r="H58" s="6">
-        <f>SUM(H56:H57)</f>
-        <v/>
-      </c>
-      <c r="I58" s="6">
-        <f>SUM(I56:I57)</f>
-        <v/>
-      </c>
-      <c r="J58" s="6">
-        <f>SUM(J56:J57)</f>
-        <v/>
-      </c>
-      <c r="K58" s="6">
-        <f>SUM(K56:K57)</f>
-        <v/>
-      </c>
-      <c r="L58" s="6">
-        <f>SUM(L56:L57)</f>
-        <v/>
-      </c>
-      <c r="M58" s="6">
-        <f>SUM(M56:M57)</f>
-        <v/>
-      </c>
-      <c r="N58" s="6">
-        <f>SUM(N56:N57)</f>
-        <v/>
-      </c>
-      <c r="O58" s="6">
-        <f>SUM(O56:O57)</f>
-        <v/>
-      </c>
-      <c r="P58" s="6">
-        <f>SUM(P56:P57)</f>
-        <v/>
-      </c>
-      <c r="Q58" s="6">
-        <f>SUM(Q56:Q57)</f>
-        <v/>
+      <c r="F58" s="6" t="n">
+        <v>64.43040000000002</v>
+      </c>
+      <c r="G58" s="6" t="n">
+        <v>59.97444495867769</v>
+      </c>
+      <c r="H58" s="6" t="n">
+        <v>63.81300297520662</v>
+      </c>
+      <c r="I58" s="6" t="n">
+        <v>64.29070413223141</v>
+      </c>
+      <c r="J58" s="6" t="n">
+        <v>71.67941950413224</v>
+      </c>
+      <c r="K58" s="6" t="n">
+        <v>75.20447603305783</v>
+      </c>
+      <c r="L58" s="6" t="n">
+        <v>93.72659900826447</v>
+      </c>
+      <c r="M58" s="6" t="n">
+        <v>100.9996601652893</v>
+      </c>
+      <c r="N58" s="6" t="n">
+        <v>92.78895867768597</v>
+      </c>
+      <c r="O58" s="6" t="n">
+        <v>94.2703338842975</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v>81.13453884297523</v>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v>82.06295404958678</v>
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
@@ -3787,53 +3725,41 @@
           <t>Total RG reported</t>
         </is>
       </c>
-      <c r="F59" s="6">
-        <f>F46*60*60*24*F$52/43560</f>
-        <v/>
-      </c>
-      <c r="G59" s="6">
-        <f>G46*60*60*24*G$52/43560</f>
-        <v/>
-      </c>
-      <c r="H59" s="6">
-        <f>H46*60*60*24*H$52/43560</f>
-        <v/>
-      </c>
-      <c r="I59" s="6">
-        <f>I46*60*60*24*I$52/43560</f>
-        <v/>
-      </c>
-      <c r="J59" s="6">
-        <f>J46*60*60*24*J$52/43560</f>
-        <v/>
-      </c>
-      <c r="K59" s="6">
-        <f>K46*60*60*24*K$52/43560</f>
-        <v/>
-      </c>
-      <c r="L59" s="6">
-        <f>L46*60*60*24*L$52/43560</f>
-        <v/>
-      </c>
-      <c r="M59" s="6">
-        <f>M46*60*60*24*M$52/43560</f>
-        <v/>
-      </c>
-      <c r="N59" s="6">
-        <f>N46*60*60*24*N$52/43560</f>
-        <v/>
-      </c>
-      <c r="O59" s="6">
-        <f>O46*60*60*24*O$52/43560</f>
-        <v/>
-      </c>
-      <c r="P59" s="6">
-        <f>P46*60*60*24*P$52/43560</f>
-        <v/>
-      </c>
-      <c r="Q59" s="6">
-        <f>Q46*60*60*24*Q$52/43560</f>
-        <v/>
+      <c r="F59" s="6" t="n">
+        <v>64.43040000000001</v>
+      </c>
+      <c r="G59" s="6" t="n">
+        <v>59.97438942148759</v>
+      </c>
+      <c r="H59" s="6" t="n">
+        <v>63.81294148760329</v>
+      </c>
+      <c r="I59" s="6" t="n">
+        <v>64.29052561983471</v>
+      </c>
+      <c r="J59" s="6" t="n">
+        <v>71.67948099173553</v>
+      </c>
+      <c r="K59" s="6" t="n">
+        <v>75.20447603305784</v>
+      </c>
+      <c r="L59" s="6" t="n">
+        <v>93.72672198347108</v>
+      </c>
+      <c r="M59" s="6" t="n">
+        <v>100.999598677686</v>
+      </c>
+      <c r="N59" s="6" t="n">
+        <v>92.78883966942151</v>
+      </c>
+      <c r="O59" s="6" t="n">
+        <v>94.2702723966942</v>
+      </c>
+      <c r="P59" s="6" t="n">
+        <v>81.13465785123967</v>
+      </c>
+      <c r="Q59" s="6" t="n">
+        <v>82.06301553719008</v>
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
@@ -3849,57 +3775,44 @@
 Buckman 1, 7, 8; Row 13, Column 11</t>
         </is>
       </c>
-      <c r="F60" s="6">
-        <f>F32*60*60*24*F$52/43560</f>
-        <v/>
-      </c>
-      <c r="G60" s="6">
-        <f>G32*60*60*24*G$52/43560</f>
-        <v/>
-      </c>
-      <c r="H60" s="6">
-        <f>H32*60*60*24*H$52/43560</f>
-        <v/>
-      </c>
-      <c r="I60" s="6">
-        <f>I32*60*60*24*I$52/43560</f>
-        <v/>
-      </c>
-      <c r="J60" s="6">
-        <f>J32*60*60*24*J$52/43560</f>
-        <v/>
-      </c>
-      <c r="K60" s="6">
-        <f>K32*60*60*24*K$52/43560</f>
-        <v/>
-      </c>
-      <c r="L60" s="6">
-        <f>L32*60*60*24*L$52/43560</f>
-        <v/>
-      </c>
-      <c r="M60" s="6">
-        <f>M32*60*60*24*M$52/43560</f>
-        <v/>
-      </c>
-      <c r="N60" s="6">
-        <f>N32*60*60*24*N$52/43560</f>
-        <v/>
-      </c>
-      <c r="O60" s="6">
-        <f>O32*60*60*24*O$52/43560</f>
-        <v/>
-      </c>
-      <c r="P60" s="6">
-        <f>P32*60*60*24*P$52/43560</f>
-        <v/>
-      </c>
-      <c r="Q60" s="6">
-        <f>Q32*60*60*24*Q$52/43560</f>
-        <v/>
-      </c>
-      <c r="R60" s="7">
-        <f>SUM(F60:Q60)</f>
-        <v/>
+      <c r="F60" s="6" t="n">
+        <v>24.6305811570248</v>
+      </c>
+      <c r="G60" s="6" t="n">
+        <v>24.19277752066115</v>
+      </c>
+      <c r="H60" s="6" t="n">
+        <v>24.42625785123967</v>
+      </c>
+      <c r="I60" s="6" t="n">
+        <v>26.31635702479339</v>
+      </c>
+      <c r="J60" s="6" t="n">
+        <v>32.44356495867769</v>
+      </c>
+      <c r="K60" s="6" t="n">
+        <v>36.9718214876033</v>
+      </c>
+      <c r="L60" s="6" t="n">
+        <v>53.60999603305785</v>
+      </c>
+      <c r="M60" s="6" t="n">
+        <v>60.16648066115702</v>
+      </c>
+      <c r="N60" s="6" t="n">
+        <v>52.84692892561984</v>
+      </c>
+      <c r="O60" s="6" t="n">
+        <v>52.70311537190083</v>
+      </c>
+      <c r="P60" s="6" t="n">
+        <v>40.92569256198347</v>
+      </c>
+      <c r="Q60" s="6" t="n">
+        <v>40.66691702479339</v>
+      </c>
+      <c r="R60" s="7" t="n">
+        <v>469.9004905785123</v>
       </c>
     </row>
   </sheetData>

--- a/buckman/output/depletion/TABLE_4_Rio_Grande_Otowi_2024.xlsx
+++ b/buckman/output/depletion/TABLE_4_Rio_Grande_Otowi_2024.xlsx
@@ -20,7 +20,7 @@
     <numFmt numFmtId="164" formatCode="0.000000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,6 +36,18 @@
     <font>
       <name val="Aptos"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00808080"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00808080"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="2">
@@ -58,7 +70,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -74,6 +86,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -439,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R60"/>
+  <dimension ref="A1:R70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3815,6 +3830,461 @@
         <v>469.9004905785123</v>
       </c>
     </row>
+    <row r="62">
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>CROSS-CHECK (formulas)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="C63" s="10" t="inlineStr">
+        <is>
+          <t>CFS SUMIF: above Otowi</t>
+        </is>
+      </c>
+      <c r="F63" s="11">
+        <f>SUMIF($R$2:$R$45,"above",F$2:F$45)-F53</f>
+        <v/>
+      </c>
+      <c r="G63" s="11">
+        <f>SUMIF($R$2:$R$45,"above",G$2:G$45)-G53</f>
+        <v/>
+      </c>
+      <c r="H63" s="11">
+        <f>SUMIF($R$2:$R$45,"above",H$2:H$45)-H53</f>
+        <v/>
+      </c>
+      <c r="I63" s="11">
+        <f>SUMIF($R$2:$R$45,"above",I$2:I$45)-I53</f>
+        <v/>
+      </c>
+      <c r="J63" s="11">
+        <f>SUMIF($R$2:$R$45,"above",J$2:J$45)-J53</f>
+        <v/>
+      </c>
+      <c r="K63" s="11">
+        <f>SUMIF($R$2:$R$45,"above",K$2:K$45)-K53</f>
+        <v/>
+      </c>
+      <c r="L63" s="11">
+        <f>SUMIF($R$2:$R$45,"above",L$2:L$45)-L53</f>
+        <v/>
+      </c>
+      <c r="M63" s="11">
+        <f>SUMIF($R$2:$R$45,"above",M$2:M$45)-M53</f>
+        <v/>
+      </c>
+      <c r="N63" s="11">
+        <f>SUMIF($R$2:$R$45,"above",N$2:N$45)-N53</f>
+        <v/>
+      </c>
+      <c r="O63" s="11">
+        <f>SUMIF($R$2:$R$45,"above",O$2:O$45)-O53</f>
+        <v/>
+      </c>
+      <c r="P63" s="11">
+        <f>SUMIF($R$2:$R$45,"above",P$2:P$45)-P53</f>
+        <v/>
+      </c>
+      <c r="Q63" s="11">
+        <f>SUMIF($R$2:$R$45,"above",Q$2:Q$45)-Q53</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="C64" s="10" t="inlineStr">
+        <is>
+          <t>CFS SUMIF: below Otowi</t>
+        </is>
+      </c>
+      <c r="F64" s="11">
+        <f>SUMIF($R$2:$R$45,"below",F$2:F$45)-F54</f>
+        <v/>
+      </c>
+      <c r="G64" s="11">
+        <f>SUMIF($R$2:$R$45,"below",G$2:G$45)-G54</f>
+        <v/>
+      </c>
+      <c r="H64" s="11">
+        <f>SUMIF($R$2:$R$45,"below",H$2:H$45)-H54</f>
+        <v/>
+      </c>
+      <c r="I64" s="11">
+        <f>SUMIF($R$2:$R$45,"below",I$2:I$45)-I54</f>
+        <v/>
+      </c>
+      <c r="J64" s="11">
+        <f>SUMIF($R$2:$R$45,"below",J$2:J$45)-J54</f>
+        <v/>
+      </c>
+      <c r="K64" s="11">
+        <f>SUMIF($R$2:$R$45,"below",K$2:K$45)-K54</f>
+        <v/>
+      </c>
+      <c r="L64" s="11">
+        <f>SUMIF($R$2:$R$45,"below",L$2:L$45)-L54</f>
+        <v/>
+      </c>
+      <c r="M64" s="11">
+        <f>SUMIF($R$2:$R$45,"below",M$2:M$45)-M54</f>
+        <v/>
+      </c>
+      <c r="N64" s="11">
+        <f>SUMIF($R$2:$R$45,"below",N$2:N$45)-N54</f>
+        <v/>
+      </c>
+      <c r="O64" s="11">
+        <f>SUMIF($R$2:$R$45,"below",O$2:O$45)-O54</f>
+        <v/>
+      </c>
+      <c r="P64" s="11">
+        <f>SUMIF($R$2:$R$45,"below",P$2:P$45)-P54</f>
+        <v/>
+      </c>
+      <c r="Q64" s="11">
+        <f>SUMIF($R$2:$R$45,"below",Q$2:Q$45)-Q54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="C65" s="10" t="inlineStr">
+        <is>
+          <t>CFS SUM: above (rows 20-29)</t>
+        </is>
+      </c>
+      <c r="F65" s="11">
+        <f>SUM(F20:F29)-F53</f>
+        <v/>
+      </c>
+      <c r="G65" s="11">
+        <f>SUM(G20:G29)-G53</f>
+        <v/>
+      </c>
+      <c r="H65" s="11">
+        <f>SUM(H20:H29)-H53</f>
+        <v/>
+      </c>
+      <c r="I65" s="11">
+        <f>SUM(I20:I29)-I53</f>
+        <v/>
+      </c>
+      <c r="J65" s="11">
+        <f>SUM(J20:J29)-J53</f>
+        <v/>
+      </c>
+      <c r="K65" s="11">
+        <f>SUM(K20:K29)-K53</f>
+        <v/>
+      </c>
+      <c r="L65" s="11">
+        <f>SUM(L20:L29)-L53</f>
+        <v/>
+      </c>
+      <c r="M65" s="11">
+        <f>SUM(M20:M29)-M53</f>
+        <v/>
+      </c>
+      <c r="N65" s="11">
+        <f>SUM(N20:N29)-N53</f>
+        <v/>
+      </c>
+      <c r="O65" s="11">
+        <f>SUM(O20:O29)-O53</f>
+        <v/>
+      </c>
+      <c r="P65" s="11">
+        <f>SUM(P20:P29)-P53</f>
+        <v/>
+      </c>
+      <c r="Q65" s="11">
+        <f>SUM(Q20:Q29)-Q53</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="C66" s="10" t="inlineStr">
+        <is>
+          <t>CFS SUM: below (rows 30-45)</t>
+        </is>
+      </c>
+      <c r="F66" s="11">
+        <f>SUM(F30:F45)-F54</f>
+        <v/>
+      </c>
+      <c r="G66" s="11">
+        <f>SUM(G30:G45)-G54</f>
+        <v/>
+      </c>
+      <c r="H66" s="11">
+        <f>SUM(H30:H45)-H54</f>
+        <v/>
+      </c>
+      <c r="I66" s="11">
+        <f>SUM(I30:I45)-I54</f>
+        <v/>
+      </c>
+      <c r="J66" s="11">
+        <f>SUM(J30:J45)-J54</f>
+        <v/>
+      </c>
+      <c r="K66" s="11">
+        <f>SUM(K30:K45)-K54</f>
+        <v/>
+      </c>
+      <c r="L66" s="11">
+        <f>SUM(L30:L45)-L54</f>
+        <v/>
+      </c>
+      <c r="M66" s="11">
+        <f>SUM(M30:M45)-M54</f>
+        <v/>
+      </c>
+      <c r="N66" s="11">
+        <f>SUM(N30:N45)-N54</f>
+        <v/>
+      </c>
+      <c r="O66" s="11">
+        <f>SUM(O30:O45)-O54</f>
+        <v/>
+      </c>
+      <c r="P66" s="11">
+        <f>SUM(P30:P45)-P54</f>
+        <v/>
+      </c>
+      <c r="Q66" s="11">
+        <f>SUM(Q30:Q45)-Q54</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="C67" s="10" t="inlineStr">
+        <is>
+          <t>AF check: above Otowi</t>
+        </is>
+      </c>
+      <c r="F67" s="11">
+        <f>F53*F52*86400/43560-F56</f>
+        <v/>
+      </c>
+      <c r="G67" s="11">
+        <f>G53*G52*86400/43560-G56</f>
+        <v/>
+      </c>
+      <c r="H67" s="11">
+        <f>H53*H52*86400/43560-H56</f>
+        <v/>
+      </c>
+      <c r="I67" s="11">
+        <f>I53*I52*86400/43560-I56</f>
+        <v/>
+      </c>
+      <c r="J67" s="11">
+        <f>J53*J52*86400/43560-J56</f>
+        <v/>
+      </c>
+      <c r="K67" s="11">
+        <f>K53*K52*86400/43560-K56</f>
+        <v/>
+      </c>
+      <c r="L67" s="11">
+        <f>L53*L52*86400/43560-L56</f>
+        <v/>
+      </c>
+      <c r="M67" s="11">
+        <f>M53*M52*86400/43560-M56</f>
+        <v/>
+      </c>
+      <c r="N67" s="11">
+        <f>N53*N52*86400/43560-N56</f>
+        <v/>
+      </c>
+      <c r="O67" s="11">
+        <f>O53*O52*86400/43560-O56</f>
+        <v/>
+      </c>
+      <c r="P67" s="11">
+        <f>P53*P52*86400/43560-P56</f>
+        <v/>
+      </c>
+      <c r="Q67" s="11">
+        <f>Q53*Q52*86400/43560-Q56</f>
+        <v/>
+      </c>
+      <c r="R67" s="11">
+        <f>SUM(F67:Q67)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="C68" s="10" t="inlineStr">
+        <is>
+          <t>AF check: below Otowi</t>
+        </is>
+      </c>
+      <c r="F68" s="11">
+        <f>F54*F52*86400/43560-F57</f>
+        <v/>
+      </c>
+      <c r="G68" s="11">
+        <f>G54*G52*86400/43560-G57</f>
+        <v/>
+      </c>
+      <c r="H68" s="11">
+        <f>H54*H52*86400/43560-H57</f>
+        <v/>
+      </c>
+      <c r="I68" s="11">
+        <f>I54*I52*86400/43560-I57</f>
+        <v/>
+      </c>
+      <c r="J68" s="11">
+        <f>J54*J52*86400/43560-J57</f>
+        <v/>
+      </c>
+      <c r="K68" s="11">
+        <f>K54*K52*86400/43560-K57</f>
+        <v/>
+      </c>
+      <c r="L68" s="11">
+        <f>L54*L52*86400/43560-L57</f>
+        <v/>
+      </c>
+      <c r="M68" s="11">
+        <f>M54*M52*86400/43560-M57</f>
+        <v/>
+      </c>
+      <c r="N68" s="11">
+        <f>N54*N52*86400/43560-N57</f>
+        <v/>
+      </c>
+      <c r="O68" s="11">
+        <f>O54*O52*86400/43560-O57</f>
+        <v/>
+      </c>
+      <c r="P68" s="11">
+        <f>P54*P52*86400/43560-P57</f>
+        <v/>
+      </c>
+      <c r="Q68" s="11">
+        <f>Q54*Q52*86400/43560-Q57</f>
+        <v/>
+      </c>
+      <c r="R68" s="11">
+        <f>SUM(F68:Q68)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="C69" s="10" t="inlineStr">
+        <is>
+          <t>Total check: above+below−sum</t>
+        </is>
+      </c>
+      <c r="F69" s="11">
+        <f>F56+F57-F58</f>
+        <v/>
+      </c>
+      <c r="G69" s="11">
+        <f>G56+G57-G58</f>
+        <v/>
+      </c>
+      <c r="H69" s="11">
+        <f>H56+H57-H58</f>
+        <v/>
+      </c>
+      <c r="I69" s="11">
+        <f>I56+I57-I58</f>
+        <v/>
+      </c>
+      <c r="J69" s="11">
+        <f>J56+J57-J58</f>
+        <v/>
+      </c>
+      <c r="K69" s="11">
+        <f>K56+K57-K58</f>
+        <v/>
+      </c>
+      <c r="L69" s="11">
+        <f>L56+L57-L58</f>
+        <v/>
+      </c>
+      <c r="M69" s="11">
+        <f>M56+M57-M58</f>
+        <v/>
+      </c>
+      <c r="N69" s="11">
+        <f>N56+N57-N58</f>
+        <v/>
+      </c>
+      <c r="O69" s="11">
+        <f>O56+O57-O58</f>
+        <v/>
+      </c>
+      <c r="P69" s="11">
+        <f>P56+P57-P58</f>
+        <v/>
+      </c>
+      <c r="Q69" s="11">
+        <f>Q56+Q57-Q58</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="C70" s="10" t="inlineStr">
+        <is>
+          <t>RG reported check: sum−sfmodflx</t>
+        </is>
+      </c>
+      <c r="F70" s="11">
+        <f>F58-F59</f>
+        <v/>
+      </c>
+      <c r="G70" s="11">
+        <f>G58-G59</f>
+        <v/>
+      </c>
+      <c r="H70" s="11">
+        <f>H58-H59</f>
+        <v/>
+      </c>
+      <c r="I70" s="11">
+        <f>I58-I59</f>
+        <v/>
+      </c>
+      <c r="J70" s="11">
+        <f>J58-J59</f>
+        <v/>
+      </c>
+      <c r="K70" s="11">
+        <f>K58-K59</f>
+        <v/>
+      </c>
+      <c r="L70" s="11">
+        <f>L58-L59</f>
+        <v/>
+      </c>
+      <c r="M70" s="11">
+        <f>M58-M59</f>
+        <v/>
+      </c>
+      <c r="N70" s="11">
+        <f>N58-N59</f>
+        <v/>
+      </c>
+      <c r="O70" s="11">
+        <f>O58-O59</f>
+        <v/>
+      </c>
+      <c r="P70" s="11">
+        <f>P58-P59</f>
+        <v/>
+      </c>
+      <c r="Q70" s="11">
+        <f>Q58-Q59</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
